--- a/template/chip-sample.xlsx
+++ b/template/chip-sample.xlsx
@@ -401,10 +401,6 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:B10"/>
-  <cols>
-    <col min="1" max="1" width="14.83203125" customWidth="1"/>
-    <col min="2" max="2" width="14.83203125" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -496,31 +492,6 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:W4"/>
-  <cols>
-    <col min="1" max="1" width="14.83203125" customWidth="1"/>
-    <col min="2" max="2" width="14.83203125" customWidth="1"/>
-    <col min="3" max="3" width="14.83203125" customWidth="1"/>
-    <col min="4" max="4" width="14.83203125" customWidth="1"/>
-    <col min="5" max="5" width="22.83203125" customWidth="1"/>
-    <col min="6" max="6" width="18.83203125" customWidth="1"/>
-    <col min="7" max="7" width="16.83203125" customWidth="1"/>
-    <col min="8" max="8" width="25.83203125" customWidth="1"/>
-    <col min="9" max="9" width="14.83203125" customWidth="1"/>
-    <col min="10" max="10" width="22.83203125" customWidth="1"/>
-    <col min="11" max="11" width="19.83203125" customWidth="1"/>
-    <col min="12" max="12" width="24.83203125" customWidth="1"/>
-    <col min="13" max="13" width="14.83203125" customWidth="1"/>
-    <col min="14" max="14" width="14.83203125" customWidth="1"/>
-    <col min="15" max="15" width="17.83203125" customWidth="1"/>
-    <col min="16" max="16" width="16.83203125" customWidth="1"/>
-    <col min="17" max="17" width="15.83203125" customWidth="1"/>
-    <col min="18" max="18" width="14.83203125" customWidth="1"/>
-    <col min="19" max="19" width="16.83203125" customWidth="1"/>
-    <col min="20" max="20" width="14.83203125" customWidth="1"/>
-    <col min="21" max="21" width="22.83203125" customWidth="1"/>
-    <col min="22" max="22" width="24.83203125" customWidth="1"/>
-    <col min="23" max="23" width="24.83203125" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -648,8 +619,8 @@
       <c r="R2">
         <v>2030</v>
       </c>
-      <c r="S2" t="str">
-        <v/>
+      <c r="S2">
+        <v>79.2</v>
       </c>
       <c r="T2" t="str">
         <v>Orange County Community Health Survey, 2024</v>
@@ -719,8 +690,8 @@
       <c r="R3">
         <v>2030</v>
       </c>
-      <c r="S3" t="str">
-        <v/>
+      <c r="S3">
+        <v>45.8</v>
       </c>
       <c r="T3" t="str">
         <v>Orange County Community Health Survey, 2024</v>
@@ -790,8 +761,8 @@
       <c r="R4">
         <v>2030</v>
       </c>
-      <c r="S4" t="str">
-        <v/>
+      <c r="S4">
+        <v>76.3</v>
       </c>
       <c r="T4" t="str">
         <v>NYS Behavioral Risk Factor Surveillance Survey (BRFSS), 2024</v>
@@ -816,16 +787,6 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:H9"/>
-  <cols>
-    <col min="1" max="1" width="15.83203125" customWidth="1"/>
-    <col min="2" max="2" width="14.83203125" customWidth="1"/>
-    <col min="3" max="3" width="15.83203125" customWidth="1"/>
-    <col min="4" max="4" width="14.83203125" customWidth="1"/>
-    <col min="5" max="5" width="14.83203125" customWidth="1"/>
-    <col min="6" max="6" width="14.83203125" customWidth="1"/>
-    <col min="7" max="7" width="14.83203125" customWidth="1"/>
-    <col min="8" max="8" width="14.83203125" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -876,7 +837,7 @@
         <v>Once</v>
       </c>
       <c r="H2" t="str">
-        <v>not_started</v>
+        <v>complete</v>
       </c>
     </row>
     <row r="3">
@@ -902,7 +863,7 @@
         <v>Quarterly</v>
       </c>
       <c r="H3" t="str">
-        <v>not_started</v>
+        <v>in_progress</v>
       </c>
     </row>
     <row r="4">
@@ -928,7 +889,7 @@
         <v>Once</v>
       </c>
       <c r="H4" t="str">
-        <v>not_started</v>
+        <v>complete</v>
       </c>
     </row>
     <row r="5">
@@ -954,7 +915,7 @@
         <v>Once</v>
       </c>
       <c r="H5" t="str">
-        <v>not_started</v>
+        <v>complete</v>
       </c>
     </row>
     <row r="6">
@@ -980,7 +941,7 @@
         <v>Quarterly</v>
       </c>
       <c r="H6" t="str">
-        <v>not_started</v>
+        <v>in_progress</v>
       </c>
     </row>
     <row r="7">
@@ -1006,7 +967,7 @@
         <v>Quarterly</v>
       </c>
       <c r="H7" t="str">
-        <v>not_started</v>
+        <v>in_progress</v>
       </c>
     </row>
     <row r="8">
@@ -1032,7 +993,7 @@
         <v>Quarterly</v>
       </c>
       <c r="H8" t="str">
-        <v>not_started</v>
+        <v>in_progress</v>
       </c>
     </row>
     <row r="9">
@@ -1071,15 +1032,6 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:G42"/>
-  <cols>
-    <col min="1" max="1" width="14.83203125" customWidth="1"/>
-    <col min="2" max="2" width="14.83203125" customWidth="1"/>
-    <col min="3" max="3" width="14.83203125" customWidth="1"/>
-    <col min="4" max="4" width="14.83203125" customWidth="1"/>
-    <col min="5" max="5" width="18.83203125" customWidth="1"/>
-    <col min="6" max="6" width="20.83203125" customWidth="1"/>
-    <col min="7" max="7" width="14.83203125" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">

--- a/template/chip-sample.xlsx
+++ b/template/chip-sample.xlsx
@@ -401,6 +401,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:B10"/>
+  <cols>
+    <col min="1" max="1" width="14.83203125" customWidth="1"/>
+    <col min="2" max="2" width="14.83203125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -491,7 +495,36 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:W4"/>
+  <dimension ref="A1:AA4"/>
+  <cols>
+    <col min="1" max="1" width="14.83203125" customWidth="1"/>
+    <col min="2" max="2" width="14.83203125" customWidth="1"/>
+    <col min="3" max="3" width="14.83203125" customWidth="1"/>
+    <col min="4" max="4" width="14.83203125" customWidth="1"/>
+    <col min="5" max="5" width="22.83203125" customWidth="1"/>
+    <col min="6" max="6" width="18.83203125" customWidth="1"/>
+    <col min="7" max="7" width="16.83203125" customWidth="1"/>
+    <col min="8" max="8" width="25.83203125" customWidth="1"/>
+    <col min="9" max="9" width="14.83203125" customWidth="1"/>
+    <col min="10" max="10" width="22.83203125" customWidth="1"/>
+    <col min="11" max="11" width="19.83203125" customWidth="1"/>
+    <col min="12" max="12" width="24.83203125" customWidth="1"/>
+    <col min="13" max="13" width="14.83203125" customWidth="1"/>
+    <col min="14" max="14" width="14.83203125" customWidth="1"/>
+    <col min="15" max="15" width="17.83203125" customWidth="1"/>
+    <col min="16" max="16" width="16.83203125" customWidth="1"/>
+    <col min="17" max="17" width="15.83203125" customWidth="1"/>
+    <col min="18" max="18" width="14.83203125" customWidth="1"/>
+    <col min="19" max="19" width="16.83203125" customWidth="1"/>
+    <col min="20" max="20" width="14.83203125" customWidth="1"/>
+    <col min="21" max="21" width="14.83203125" customWidth="1"/>
+    <col min="22" max="22" width="21.83203125" customWidth="1"/>
+    <col min="23" max="23" width="14.83203125" customWidth="1"/>
+    <col min="24" max="24" width="14.83203125" customWidth="1"/>
+    <col min="25" max="25" width="22.83203125" customWidth="1"/>
+    <col min="26" max="26" width="24.83203125" customWidth="1"/>
+    <col min="27" max="27" width="24.83203125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -552,15 +585,27 @@
         <v>currentValue</v>
       </c>
       <c r="T1" t="str">
+        <v>asOfDate</v>
+      </c>
+      <c r="U1" t="str">
+        <v>source</v>
+      </c>
+      <c r="V1" t="str">
+        <v>refreshCycleYears</v>
+      </c>
+      <c r="W1" t="str">
+        <v>direction</v>
+      </c>
+      <c r="X1" t="str">
         <v>dataSource</v>
       </c>
-      <c r="U1" t="str">
+      <c r="Y1" t="str">
         <v>reportingFrequency</v>
       </c>
-      <c r="V1" t="str">
+      <c r="Z1" t="str">
         <v>stateComparisonValue</v>
       </c>
-      <c r="W1" t="str">
+      <c r="AA1" t="str">
         <v>stateComparisonLabel</v>
       </c>
     </row>
@@ -619,19 +664,31 @@
       <c r="R2">
         <v>2030</v>
       </c>
-      <c r="S2">
-        <v>79.2</v>
+      <c r="S2" t="str">
+        <v/>
       </c>
       <c r="T2" t="str">
+        <v/>
+      </c>
+      <c r="U2" t="str">
+        <v/>
+      </c>
+      <c r="V2">
+        <v>3</v>
+      </c>
+      <c r="W2" t="str">
+        <v>higher_is_better</v>
+      </c>
+      <c r="X2" t="str">
         <v>Orange County Community Health Survey, 2024</v>
       </c>
-      <c r="U2" t="str">
+      <c r="Y2" t="str">
         <v>Every 3 years</v>
       </c>
-      <c r="V2">
+      <c r="Z2">
         <v>51.1</v>
       </c>
-      <c r="W2" t="str">
+      <c r="AA2" t="str">
         <v>NYSDOH Prevention Agenda (State-Level)</v>
       </c>
     </row>
@@ -690,19 +747,31 @@
       <c r="R3">
         <v>2030</v>
       </c>
-      <c r="S3">
-        <v>45.8</v>
+      <c r="S3" t="str">
+        <v/>
       </c>
       <c r="T3" t="str">
+        <v/>
+      </c>
+      <c r="U3" t="str">
+        <v/>
+      </c>
+      <c r="V3">
+        <v>1</v>
+      </c>
+      <c r="W3" t="str">
+        <v>lower_is_better</v>
+      </c>
+      <c r="X3" t="str">
         <v>Orange County Community Health Survey, 2024</v>
       </c>
-      <c r="U3" t="str">
+      <c r="Y3" t="str">
         <v>Yearly</v>
       </c>
-      <c r="V3">
+      <c r="Z3">
         <v>18.9</v>
       </c>
-      <c r="W3" t="str">
+      <c r="AA3" t="str">
         <v>NYSDOH Prevention Agenda goal by 2030</v>
       </c>
     </row>
@@ -761,32 +830,55 @@
       <c r="R4">
         <v>2030</v>
       </c>
-      <c r="S4">
-        <v>76.3</v>
+      <c r="S4" t="str">
+        <v/>
       </c>
       <c r="T4" t="str">
+        <v/>
+      </c>
+      <c r="U4" t="str">
+        <v/>
+      </c>
+      <c r="V4">
+        <v>4</v>
+      </c>
+      <c r="W4" t="str">
+        <v>higher_is_better</v>
+      </c>
+      <c r="X4" t="str">
         <v>NYS Behavioral Risk Factor Surveillance Survey (BRFSS), 2024</v>
       </c>
-      <c r="U4" t="str">
+      <c r="Y4" t="str">
         <v>Every 4 years</v>
       </c>
-      <c r="V4">
+      <c r="Z4">
         <v>83.5</v>
       </c>
-      <c r="W4" t="str">
+      <c r="AA4" t="str">
         <v>NYSDOH Prevention Agenda goal by 2030</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:W4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:AA4"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:I9"/>
+  <cols>
+    <col min="1" max="1" width="15.83203125" customWidth="1"/>
+    <col min="2" max="2" width="14.83203125" customWidth="1"/>
+    <col min="3" max="3" width="15.83203125" customWidth="1"/>
+    <col min="4" max="4" width="14.83203125" customWidth="1"/>
+    <col min="5" max="5" width="14.83203125" customWidth="1"/>
+    <col min="6" max="6" width="14.83203125" customWidth="1"/>
+    <col min="7" max="7" width="14.83203125" customWidth="1"/>
+    <col min="8" max="8" width="14.83203125" customWidth="1"/>
+    <col min="9" max="9" width="15.83203125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -813,6 +905,9 @@
       <c r="H1" t="str">
         <v>status</v>
       </c>
+      <c r="I1" t="str">
+        <v>lastUpdated</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
@@ -839,6 +934,9 @@
       <c r="H2" t="str">
         <v>complete</v>
       </c>
+      <c r="I2" t="str">
+        <v>2026-08-15</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
@@ -865,6 +963,9 @@
       <c r="H3" t="str">
         <v>in_progress</v>
       </c>
+      <c r="I3" t="str">
+        <v>2026-08-22</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
@@ -891,6 +992,9 @@
       <c r="H4" t="str">
         <v>complete</v>
       </c>
+      <c r="I4" t="str">
+        <v>2026-07-20</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
@@ -917,6 +1021,9 @@
       <c r="H5" t="str">
         <v>complete</v>
       </c>
+      <c r="I5" t="str">
+        <v>2026-08-01</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
@@ -943,6 +1050,9 @@
       <c r="H6" t="str">
         <v>in_progress</v>
       </c>
+      <c r="I6" t="str">
+        <v>2026-08-28</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
@@ -969,6 +1079,9 @@
       <c r="H7" t="str">
         <v>in_progress</v>
       </c>
+      <c r="I7" t="str">
+        <v>2026-08-10</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
@@ -995,6 +1108,9 @@
       <c r="H8" t="str">
         <v>in_progress</v>
       </c>
+      <c r="I8" t="str">
+        <v>2026-08-10</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
@@ -1021,10 +1137,13 @@
       <c r="H9" t="str">
         <v>not_started</v>
       </c>
+      <c r="I9" t="str">
+        <v/>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H9"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I9"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1032,6 +1151,15 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:G42"/>
+  <cols>
+    <col min="1" max="1" width="14.83203125" customWidth="1"/>
+    <col min="2" max="2" width="14.83203125" customWidth="1"/>
+    <col min="3" max="3" width="14.83203125" customWidth="1"/>
+    <col min="4" max="4" width="14.83203125" customWidth="1"/>
+    <col min="5" max="5" width="18.83203125" customWidth="1"/>
+    <col min="6" max="6" width="20.83203125" customWidth="1"/>
+    <col min="7" max="7" width="14.83203125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
